--- a/denodo_agent_poc/data/results/dq_agent_insights.xlsx
+++ b/denodo_agent_poc/data/results/dq_agent_insights.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28T12:26:18.226568+00:00</t>
+          <t>2026-07-29T05:57:05.854509+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
